--- a/読み解きワークショップ設計.xlsx
+++ b/読み解きワークショップ設計.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="進行表(90分)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="参加フック設計" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="素材リスト" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="自走化キット" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="概要・効果測定" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="接続設計" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="デブリーフシート雛形" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="参加フック設計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="素材リスト" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="自走化キット" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="概要・効果測定" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'素材リスト'!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'素材リスト'!$A$3:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +66,13 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7A87"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +97,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE7E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,25 +200,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -576,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -592,28 +613,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>読み解きワークショップ 進行表（標準90分）v0.2</t>
+          <t>読み解きワークショップ 進行表（標準90分＋決裁者デブリーフ15分）v0.3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>対象：Tier1の少人数チーム（5〜15名）。参加型に更新：個人→ペア→全体の段差設計、15〜20分ごとに体か形式を動かす。初回は当方ファシリ、2回目以降は自走キットで店長・リーダーが実施。</t>
+          <t>対象：Tier1の少人数チーム（5〜15名）。個人→ペア→全体の段差設計、15〜20分ごとに体か形式を動かす。M6は現場スタッフ退室後、決裁者のみで実施（売る場所を分ける）。初回は当方ファシリ、2回目以降は自走キットで店長・リーダーが実施。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>事前準備：① 全員が無料診断（9問）を受診し結果画面を持参 ② ファシリは全員のタイプを集計し、床の2軸マップ（狭い場合は卓上版）を準備 ③ 店長・オーナーへ2つの事前依頼（冒頭の「開催の意図」ひとこと／チェックインとトリセツで先に話す役）</t>
+          <t>事前準備：① 全員が無料診断（9問）を受診し結果画面を持参 ② ファシリは全員のタイプを集計し、床の2軸マップ（狭い場合は卓上版）を準備 ③ 店長・オーナーへ2つの事前依頼（冒頭の「開催の意図」ひとこと／チェックインとトリセツで先に話す役）＋WS後に15分残ってもらう約束</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>進行の弧：つかみ（安全と好奇心）→ 自分ごと化 → 相互理解 → 現場での一手 → 定着の仕掛け。発言は必ず「個人で書く→ペアで話す→全体で共有」の順に段差を作る。</t>
+          <t>進行の弧：つかみ（安全と好奇心）→ 自分ごと化 → 相互理解 → 現場での一手 → 定着の仕掛け → 決裁者への接続。発言は必ず「個人で書く→ペアで話す→全体で共有」の順に段差を作る。</t>
         </is>
       </c>
     </row>
@@ -669,8 +690,10 @@
       <c r="B7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>12</v>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -715,8 +738,10 @@
       <c r="B8" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>24</v>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -749,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="126" customHeight="1">
+    <row r="9" ht="132" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>M2 タイプ予想→人間マップ</t>
@@ -758,8 +783,10 @@
       <c r="B9" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>40</v>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
@@ -790,11 +817,11 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>個人名でなく「タイプ」で語る練習。「良い悪いでなく、うちはこういう地図」。狭い店内は模造紙の卓上版でOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="104" customHeight="1">
+          <t>個人名でなく「タイプ」で語る練習。「良い悪いでなく、うちはこういう地図」。狭い店内は模造紙の卓上版でOK。種まき：「この地図、人が入れ替わると変わります」と一言添える（再診断の種）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>M3 トリセツ交換</t>
@@ -803,8 +830,10 @@
       <c r="B10" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="9" t="n">
-        <v>58</v>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -833,11 +862,11 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>「直してほしい所」でなく「扱い方」を話す場。受け取る側のルールを徹底し、吊し上げにさせない</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="126" customHeight="1">
+          <t>「直してほしい所」でなく「扱い方」を話す場。受け取る側のルールを徹底し、吊し上げにさせない。マネジメント寄りの問いが出たら「店長の宿題として後で」とパーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>M4 現場シーンで一手</t>
@@ -846,8 +875,10 @@
       <c r="B11" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>78</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
@@ -879,11 +910,11 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>抽象論で終わらせない。「明日のシフトでできる」サイズまで小さくするのがコツ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="104" customHeight="1">
+          <t>抽象論で終わらせない。「明日のシフトでできる」サイズまで小さくするのがコツ。店長の悩みはその場で解かず、デブリーフの議題へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>M5 宣言・約束・次へ</t>
@@ -892,46 +923,48 @@
       <c r="B12" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>90</v>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>公開の宣言とチームの約束で持ち帰りを固定し、単発で終わらせない仕掛けを置く</t>
+          <t>公開の宣言とチームの約束で持ち帰りを固定し、変化の予告で「続きがある」状態を作る</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
           <t>1. 一人一言「明日から試す一手」を宣言（1人15秒）（4分）
 2. チームの約束を2〜3個決め、約束ボードに書く（進める前にひと呼吸／小さなNOを言っていい 等）（4分）
-3. 2週間後のひと言チェックイン（朝礼で「一手やってみてどうだった？」）を予告（1分）
-4. アンケート記入＋次の案内（自走キット・店長1on1・エグゼセッション）（3分）</t>
+3. 変化の予告（これから起きる3つのこと）：①熱は2週間で下がる、だから約束ボードと2週間後チェックイン ②人が替わると地図は変わる、新しい人にも診断を ③効果の見える化は四半期の匿名サーベイの役目（2分）
+4. アンケート記入（末尾に「深掘りしたいこと」チェック：自分のマネジメント／特定の相手との関係／家族でもやりたい）＋締めの一言（2分）</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
           <t>みんなの前での宣言（一貫性）
-約束ボードを現場に貼る（環境に残す）
-2週間後の締切効果</t>
+約束ボード（環境に残す）
+変化の予告（予告→的中の種）</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>ワークシートC
 約束ボード
-アンケート</t>
+アンケート（深掘りチェック付き）</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>約束はチームの共通言語として現場に残す。ボードはバックヤードなど毎日目に入る場所へ</t>
+          <t>予告は営業でなく誠実な見立てとして話す。現場の前で商品名を出すのはここまで、売るのはデブリーフで</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>合計（WS本体）</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
@@ -944,11 +977,66 @@
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
     </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>▼ WS終了直後（現場スタッフ退室後・決裁者のみ。休憩を挟まず続けて実施）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="126" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>M6 決裁者デブリーフ</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>+15</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>決裁者だけに、地図の読み解きと「これから起きること→処方」を接続し、継続の合意を作る（アップセルの本番はここ。現場の前では売らない）</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1. 今日の読み解き3つ：チームの強み1つ／火種1つ／店長ご自身の型1つ（タイプの力学に限定、人格評価にしない）（6分）
+2. これから起きる3つのこと：熱は2週間で下がる／人が替わると地図が変わる／見えた火種は放置で再燃（3分）
+3. デブリーフシートの処方対応表を渡して説明：2週間後チェックイン（無料）→四半期サーベイ→エグゼセッション／新人時の再診断（3分）
+4. CTAは1つだけ提案し、次回接点（2週間後フォロー）の日程をその場で確定（3分）</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>自チームの実データで読み解き（専門性の証明）
+予告→的中の種まき
+CTAは1つ（選択肢過多を避ける）</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>タイプ地図（当日実データ）
+デブリーフシート
+アンケート集計（深掘りチェック）</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>「今日見えたものは、放っておくと見えなくなります」。メニューを並べず、相手の痛みに合わせて処方を1つ。日程まで決めて終える</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -958,11 +1046,916 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFF3D6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>接続設計（WS後の予測マップと商品ラダー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>アップセルOKのマインドは説得でなく「予告→的中→打ち手」の体験で作る。決裁者が『この商品群が今後も必要だ』と納得する動線の設計。M5とM6、2週間後フォローが実装箇所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>■ 決裁者（店長・オーナー）の予測マップ：WS後に頭に浮かぶこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>いつ</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>決裁者の心の声（懸念・不安）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>打ち手（商品）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>接続の仕方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>直後</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>「盛り上がったが、一過性では？」</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>約束ボード＋2週間後チェックイン（自走キット同梱・無料）</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>M5で「熱は2週間で下がります」と先に予告しておく。予告済みだから不安でなく「想定内＋打ち手あり」になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>直後</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>「あの2人の火種、根が深そうだ」</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>個別の読み解き／エグゼクティブセッション</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>M6デブリーフで、タイプ地図から火種を1つだけ読み解いて見せる（力学として。人格評価にしない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>直後〜数日</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>「自分の関わり方は合っているのか。部下には聞けない」</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>エグゼクティブマインドセッション（1on1）</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>M6で店長ご自身の型の読み解きを1つだけ見せ「続きは1on1で」。買い手個人のメリットに接続</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>2週間後</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>「約束、続いているのか？」</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>当方からのフォロー連絡（無料）</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>チェックイン結果を聞く接点＝2度目の商談機会。予告の的中をここで一緒に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1〜3ヶ月</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>「効果が出ているのか、数字で見たい」</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>四半期の匿名サーベイ（働きやすさ・チームワーク）</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>M5とM6で「効果の見える化はサーベイの役目」と役割分担を予告済みにしておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>「新人が入った。また馴染めず辞めるかも」</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>新メンバー診断＋ミニ読み解き／2回目WS（自走伴走）</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>「地図は人が替わると変わる」をM2とM6で予告。オンボーディング用途として自然に再登場</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>■ 現場（スタッフ）の予測マップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>いつ</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>現場の心の声</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>打ち手</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>接続の仕方</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>翌日〜</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>「今日は言えたけど、結局同じ日常では」</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>約束ボード＋2週間後の朝礼チェックイン</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>毎日目に入る掲示と近い締切で行動を維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>直後</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>「タイプをレッテルや評価に使われないか」</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>運用ルール（評価に使わない・共有範囲は本人主導）</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>M0のグランドルールで宣言済み。自走キットのFAQにも明記</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>直後〜</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>「家族やパートナーにもやってみたい」</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>結果画面「大切な人にも」導線（B2C波及）</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>売り込まず好奇心に乗せる。法人には従業員満足の付加価値として説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>■ 接続の3原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>1. 予告 → 的中 → 打ち手：M5・M6で「これから起きること」を誠実に予告し、2週間後フォローで的中を一緒に確認してから処方を出す。予告が当たるたび「この人たちには見えている」が積み上がる（信頼の複利）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>2. 診断 → 処方の医師モデル：商品をメニューとして並べない。予測される事態への処方として、相手の痛みに合わせて1つだけ出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>3. 売る場所を分ける：現場スタッフの前では売らない（M5の「次の案内」一言まで）。本番はM6デブリーフ15分。現場の信頼（安心して配れる場）こそが商品の土台</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>■ 商品ラダー（接続の時系列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>段</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>タイミング</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>収益</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>当日90分</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>読み解きワークショップ（M0〜M5）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>体験と共通言語づくり。現場の信頼を得る</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>軽め商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>直後15分</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>M6 決裁者デブリーフ：読み解き3つ＋処方対応表＋CTA1つ＋次回日程確定</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>接続の本番。継続の合意を作る</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>無料（受注の芽）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>2週間後</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>フォロー連絡：チェックイン結果を聞く→予告の的中を確認→サーベイ提案</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>2度目の商談機会</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>無料→受注</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>四半期</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>匿名サーベイ＋ミニWS（自走伴走）</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>定点観測と定着。年間契約の根拠づくり</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>継続課金の芽</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>新メンバー診断＋ミニ読み解き／2回目WS</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>オンボーディング需要で自然に再登場</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>都度</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>深化</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>エグゼクティブマインドセッション → 年間契約</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>高額商品。決裁者個人のメリット</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>高額</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>■ M6のCTA選択ルール（1つだけ出す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>・主痛みが離職・人間関係の火種 → 四半期サーベイ＋個別の読み解き</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>・主痛みが自分のマネジメント → エグゼクティブセッション体験（店長1on1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>・迷いが見える → その場で押さず、2週間後フォローの日程だけ確定（無料）。そこで決める</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>・アンケートの「深掘りしたいこと」チェックの集計が、CTA選択とフォロー連絡の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>■ ガードレール（信頼を壊さないための線引き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>・現場スタッフの前で商品名を出すのはM5の「次の案内」一言まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>・読み解きはタイプの力学に限定する。個人の人格評価・詮索にしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>・予告は断定でなく「よくあるパターン」として誠実に話す（外れたら外れたと言う）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>・M6で決まらなくても追わない。本命は2週間後フォロー（的中確認後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>・タイプ情報の扱いは本人主導の原則を守る（全社共有は匿名分布まで）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FBE7E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>デブリーフシート（WS直後15分・店長／オーナー用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M6で使うA4 1枚。①②は当日ファシリが手書き、③は印字済みで渡す。置いていくことで「予測と処方」が手元に残る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>① 実施メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>実施日／チーム／人数</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>（記入欄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>チームのタイプ地図</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>（当日の床マップの配置をメモ。偏り・空白も）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>② 今日の読み解き3つ（ファシリが当日手書き）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>1. チームの強み</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>（例：GBS×GBLの土台が堅く、危機に強い 等。タイプの力学として書く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2. 火種（すれ違いの種）</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>（例：OBLの直球をGKSが飲み込みがち。放置すると静かな離職の型 等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>3. 店長ご自身の型と一手</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>（例：店長はOBL。圧で本音が止まる場面あり。先に「どう思う？」の問いかけを 等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>③ これから起きること → 処方（印字済みで渡す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>これから起きること（よくあるパターン）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>処方（打ち手）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>商品／費用感</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2週間ほどで熱が下がり、日常に戻っていく</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>約束ボード＋2週間後の朝礼ひと言チェックイン</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>自走キットに同梱（無料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>人の入替えで、チームの地図が変わる</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>新メンバーの診断＋ミニ読み解き（オンボーディング）</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>診断は無料／読み解きは（要確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>今日見えた火種は、放置すると再燃する</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>個別の読み解き／エグゼクティブマインドセッション（1on1）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>（要確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>「効果が出ているのか」が見えなくなる</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>四半期の匿名サーベイ（働きやすさ・チームワークの定点）</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>（要確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>④ 次の一歩（1つだけ決める）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>□ 四半期サーベイ＋個別の読み解き（離職・火種が主痛みのとき）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>□ エグゼクティブセッション体験・店長1on1（ご自身の関わり方が主題のとき）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>□ まずは2週間後フォローで決める（無料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>次回接点の日程・方法</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>（2週間後フォロー：日付／電話・LINE・訪問。その場で確定して書き込む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>※ 読み解きはタイプの力学に限定し、人格評価にしない。予告は「よくあるパターン」として誠実に。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FBE7E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1263,6 +2256,31 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>変化の予告（これから起きる3つのこと）</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>M5・M6</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>予告が的中するたび「この人たちには見えている」が積み上がる（信頼の複利）。不安の先回りは誠実さとして伝わる</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>断定せず「よくあるパターン」として話す。2週間後フォローで的中を一緒に確認して回収する</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
@@ -1272,14 +2290,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F8F88"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1300,7 +2318,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>多くは既存資産の再利用で組める。『作成状態』を更新して制作トラッカーとして使う。★＝v0.2で追加（参加フック用）。</t>
+          <t>多くは既存資産の再利用で組める。『作成状態』を更新して制作トラッカーとして使う。★＝v0.2追加（参加フック用）、◆＝v0.3追加（接続用）。</t>
         </is>
       </c>
     </row>
@@ -1337,7 +2355,7 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1357,7 +2375,7 @@
       <c r="F4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1381,7 +2399,7 @@
       <c r="F5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1405,7 +2423,7 @@
       <c r="F6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1433,7 +2451,7 @@
       <c r="F7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1461,7 +2479,7 @@
       <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1489,7 +2507,7 @@
       <c r="F9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1513,7 +2531,7 @@
       <c r="F10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1530,14 +2548,14 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>宣言・約束・2週間後チェックイン予告・次の案内</t>
+          <t>宣言・約束・変化の予告・2週間後チェックイン予告・次の案内</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>ワークシート</t>
         </is>
@@ -1565,7 +2583,7 @@
       <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>ワークシート</t>
         </is>
@@ -1593,7 +2611,7 @@
       <c r="F13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>ワークシート</t>
         </is>
@@ -1621,224 +2639,308 @@
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>ワークシート</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>アンケート（深掘りチェック付き）</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>満足度・理解度＋深掘りしたいこと（自分のマネジメント／特定の相手との関係／家族でもやりたい）</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>新規作成。集計がM6のCTA選択とフォロー連絡の材料に</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>グランドルール札</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>違い／ここだけ／受け取る／パス可（M0で掲示）</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>トリセツカード（8タイプ）</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>こう接すると/気づいてほしい/心を開く/誤解しないで</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>all-types.html（TORISET）</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>シーンカード</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>現場のあるある摩擦。Tier1業種別＋事前ヒアリングで差し替え</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>法人ポジショニング.md（消耗パターン）</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>チェックイン問いカード</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>仕事と無関係の軽い問い10種（例：最近ちょっと嬉しかったこと）</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>新規作成</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>タイプ予想メモ</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>ペア相手が床のどこに立つかを予想して書く小片（外れてOK）</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>新規作成</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>フロア2軸マップ</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>床に養生テープで2軸＋コーナー札4枚。狭い場合は模造紙の卓上版＋付箋</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>旧タイプ地図テンプレートを更新</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>約束ボード</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>チームの約束2〜3個を書いてバックヤードに掲示（A3）</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>新規作成</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>2週間後チェックインシート</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>朝礼用。一手をやってみてどうだったか一言ずつ確認</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>新規作成</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>デブリーフシート</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>実施メモ＋読み解き3つ＋処方対応表＋次の一歩（M6用・A4 1枚）</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>シート『デブリーフシート雛形』</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>フォロー連絡トークメモ</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>2週間後の電話/LINE：チェックイン結果を聞く→予告の的中を確認→サーベイ提案</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>新規作成。接続設計シート参照</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:F3"/>
@@ -1847,7 +2949,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4:F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未着手,作成中,完成,流用でOK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1855,7 +2957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F8F88"/>
@@ -1881,7 +2983,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>初回ファシリの型をそのままキット化。属人性を排し店内で品質を再現する（Funnel 1 のスケールの肝）。</t>
+          <t>初回ファシリの型をそのままキット化。属人性を排し店内で品質を再現する（Funnel 1 のスケールの肝）。※M6デブリーフとフォロー連絡は当方の営業動線なのでキットに含めない。</t>
         </is>
       </c>
     </row>
@@ -1913,7 +3015,7 @@
           <t>①</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>ファシリ台本（読み上げ式）</t>
         </is>
@@ -1931,7 +3033,7 @@
           <t>②</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
@@ -1949,14 +3051,14 @@
           <t>③</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>ワークシート印刷用PDF</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>A（自分を知る）／B（トリセツ交換）／C（一手と約束）</t>
+          <t>A（自分を知る）／B（トリセツ交換）／C（一手と約束）＋アンケート</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
@@ -1967,7 +3069,7 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>カード類</t>
         </is>
@@ -1985,7 +3087,7 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>困ったときFAQ</t>
         </is>
@@ -2003,7 +3105,7 @@
           <t>⑥</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>事前準備チェックリスト</t>
         </is>
@@ -2021,7 +3123,7 @@
           <t>⑦</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>約束ボード＋フォロー運用メモ</t>
         </is>
@@ -2055,14 +3157,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F8F88"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2073,19 +3175,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>読み解きワークショップ 概要・効果測定 v0.2</t>
+          <t>読み解きワークショップ 概要・効果測定 v0.3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出所：法人ポジショニング.md／ファネル図.md／相性ルール.md。v0.2で参加設計の5原則と定着フォローを追加。</t>
+          <t>出所：法人ポジショニング.md／ファネル図.md／相性ルール.md。v0.2で参加設計の5原則と定着フォロー、v0.3で決裁者デブリーフ（M6）と接続設計を追加。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>■ 概要</t>
         </is>
@@ -2097,12 +3199,12 @@
           <t>中心価値</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>自律的に尊重し合えるチームワークを構築する</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n"/>
+      <c r="C5" s="21" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -2110,12 +3212,12 @@
           <t>3つのゴール</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>① 自分を知る（強みと癖を言葉に）／② 相手を知る（タイプ地図で共通言語）／③ 一手を持つ（自分×相手の関わり方を1つ決めて帰る）</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n"/>
+      <c r="C6" s="21" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -2123,12 +3225,12 @@
           <t>やらないこと</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>優劣づけ・人事評価・吊し上げをしない。課題は欠陥でなく『強みの裏面』として扱う（全社に安心して配れる設計の核）</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="21" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -2136,12 +3238,12 @@
           <t>進行の弧</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>つかみ（安全と好奇心）→ 自分ごと化 → 相互理解 → 現場での一手 → 定着の仕掛け</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="n"/>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>つかみ（安全と好奇心）→ 自分ごと化 → 相互理解 → 現場での一手 → 定着の仕掛け → 決裁者への接続（M6）</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -2149,12 +3251,12 @@
           <t>対象</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Tier1：接客・飲食・宿・美容・介護・保育・式場などの少人数チーム</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n"/>
+      <c r="C9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -2162,12 +3264,12 @@
           <t>規模／所要／場所</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>5〜15名（15名超は分割）／標準90分（半日・60分デモに拡張可）／バックヤード等・投影でも印刷でも可</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>5〜15名（15名超は分割）／標準90分＋決裁者デブリーフ15分／バックヤード等・投影でも印刷でも可</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -2175,57 +3277,57 @@
           <t>ファシリ</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>初回は当方が担当。2回目以降は店長・リーダーが自走キットで実施</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>初回は当方が担当。2回目以降は店長・リーダーが自走キットで実施（M6と2週間後フォローは当方が継続）</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>■ 参加設計の5原則（少人数・参加型のベストプラクティス）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>1. 最初の10分で全員が一度声を出す（最初に話した人はその後も話す。発言の初速を作る）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>2. 発言は「個人で書く→ペアで話す→全体で共有」の順に段差を作る（いきなり全体で聞かない）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>3. 15〜20分に一度、体か形式を動かす（立つ・歩く・ペア替え。座学を続けない）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4. スライドより具体物で手と体を使う（カード・床マップ・ボード。見せる時間より触る時間）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>5. 安全弁を先に配る（パス可・共有範囲は本人が選ぶ）。逃げ道があるから、人は踏み込める</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>■ 効果測定（診断でなく別立ての軽い指標で映す）</t>
         </is>
@@ -2249,24 +3351,24 @@
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>短期（WS直後）</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>満足度／『相手を理解できた』『関わり方のヒントを得た』回答率／受診率</t>
+          <t>満足度／『相手を理解できた』『関わり方のヒントを得た』回答率／受診率／深掘りチェックの回答</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>アンケートで取得</t>
+          <t>アンケートで取得。深掘りチェックはM6のCTA選択とフォロー連絡の材料</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>定着（2週間後）</t>
         </is>
@@ -2278,12 +3380,12 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>店長が実施（自走キット⑦の運用メモ）</t>
+          <t>店長が実施（自走キット⑦）。当方フォロー連絡で結果を聞く＝2度目の商談機会</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>中期（四半期）</t>
         </is>
@@ -2300,7 +3402,7 @@
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>次への橋</t>
         </is>
@@ -2312,12 +3414,12 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>高額商品・B2C波及・年間契約へ</t>
+          <t>接続の設計は『接続設計』シート参照</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>■ 時間バリエーション</t>
         </is>
@@ -2341,14 +3443,14 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>標準版</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>90分・M0〜M5（本骨格）</t>
+          <t>90分＋デブリーフ15分・M0〜M6（本骨格）</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -2358,14 +3460,14 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>じっくり版</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>約3時間・M3とM4を拡張＋シーン再現ロールプレイ＋約束の運用設計まで</t>
+          <t>約3時間＋デブリーフ・M3とM4を拡張＋シーン再現ロールプレイ＋約束の運用設計まで</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2375,14 +3477,14 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>お試し版</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>約60分・M0→M1→M2（卓上版）→ミニM4→宣言</t>
+          <t>約60分・M0→M1→M2（卓上版）→ミニM4→宣言。デブリーフは商談を兼ねる</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2392,118 +3494,144 @@
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>■ 未確定事項（M2実施で検証）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>標準所要時間（90分で足りるか・モジュール配分）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>価格（現場の原資に合わせて右サイズに）</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>グループ最大人数と分割ルール</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>シーンカードの業種別バリエーション数（事前ヒアリング項目含む）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>タイプ予想ゲームの切替基準（関係性が浅い・人数が多い場合は卓上版や省略も）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>チェックイン問いのバリエーション（現場で滑らない問いの検証）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>スライド投影か印刷のみか（現場設備により選択可能に）</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>□</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>アンケート設問の最終形（法人ポジショニング.md の効果測定と接続）</t>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>アンケート設問の最終形（深掘りチェック含む。法人ポジショニング.md の効果測定と接続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>M6デブリーフの15分で足りるか／CTA別の成約率（予告→的中→打ち手の検証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>処方対応表の価格欄（要確定）の確定</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="B8:C8"/>
